--- a/game_config/Datas/QuestConfig.xlsx
+++ b/game_config/Datas/QuestConfig.xlsx
@@ -337,7 +337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="9.109375" customWidth="1" style="3" min="1" max="1"/>
@@ -777,6 +777,52 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>5006</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>收集怪物徽记</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>从怪物尸体中拾取5个怪物徽记。</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5106</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>GrantItem</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1001,5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
